--- a/visor/public/entregables/Libro_de_datos_El_miedo_que_no_baja.xlsx
+++ b/visor/public/entregables/Libro_de_datos_El_miedo_que_no_baja.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafal\OneDrive\Desktop\Projects\datajam-miedo-que-no-baja\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADAF67FB-8B8F-46F2-8B36-57F65427DE2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1325D0F-E3FF-4EF4-8DCF-95CE9B683956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="1860" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portada" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
     <sheet name="Datos_escenarios" sheetId="13" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">Cifra_oculta!$A$1:$O$64</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">Cifra_oculta!$A$1:$O$65</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">Genero!$A$1:$I$77</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">Indice_brecha!$A$1:$O$54</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">Modelos!$A$1:$Q$107</definedName>
@@ -111,7 +111,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="660">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1330" uniqueCount="661">
   <si>
     <t>BOGOTÁ DATAJAM 5  ·  2026  ·  LIBRO DE DATOS</t>
   </si>
@@ -311,7 +311,7 @@
     <t>GÉNERO · EMV 2024</t>
   </si>
   <si>
-    <t>TERRITORIO · VALIDACIÓN</t>
+    <t>TERRITORIO · CONTROL</t>
   </si>
   <si>
     <t>PREDICCIÓN · AUC</t>
@@ -323,7 +323,7 @@
     <t>de temor al acoso sexual por ser mujer, a igual edad, estrato y victimización (IC 95 % 12,9 a 23,4).</t>
   </si>
   <si>
-    <t>entre el Índice de Brecha y la cifra oculta (Spearman, IC 95 % 0,41 a 0,88; p ajustado = 0,004).</t>
+    <t>entre el Índice de Brecha y la cifra oculta al controlar el delito registrado: la de 0,72 era mecánica, porque ambos usan el mismo registro.</t>
   </si>
   <si>
     <t>de AUC al sumar el delito registrado al perfil (0,609 → 0,611); con el entorno llega a 0,782.</t>
@@ -347,7 +347,7 @@
     <t>La ciudad no ve buena parte de su delito.</t>
   </si>
   <si>
-    <t>Hay unas 5,6 víctimas por cada delito de alto impacto registrado, de 10,6 en Bosa a 0,7 en Los Mártires. El Índice de Brecha crece donde más se subregistra: ρ = 0,72 (IC 95 % 0,41 a 0,88; p ajustado = 0,004), la única relación territorial que sobrevive a la corrección por pruebas múltiples.</t>
+    <t>Hay unas 5,6 víctimas por cada delito de alto impacto registrado, de 10,6 en Bosa a 0,7 en Los Mártires. Las víctimas que reporta la encuesta no siguen al delito registrado entre localidades (ρ = 0,03). La relación entre el Índice de Brecha y la cifra oculta (ρ = 0,72) es mecánica: al controlar el delito registrado queda en -0,02.</t>
   </si>
   <si>
     <t>El barrio se siente por lo que pasa en él.</t>
@@ -728,10 +728,13 @@
     <t>Barrio inseguro (EMV) vs zona insegura (Bienal)</t>
   </si>
   <si>
+    <t>Zona insegura (Bienal) vs cifra oculta (víctimas por delito registrado)</t>
+  </si>
+  <si>
     <t>Índice de Brecha vs cifra oculta (víctimas por delito registrado)</t>
   </si>
   <si>
-    <t>Solo la relación entre el Índice de Brecha y la cifra oculta sobrevive a la corrección por pruebas múltiples. Fuente: outputs/tablas/validaciones.csv (IC por bootstrap de 2.000 réplicas).</t>
+    <t>La relación entre el Índice de Brecha y la cifra oculta sobrevive a la corrección, pero es mecánica: los dos usan el delito registrado y, al controlarlo, la correlación parcial es prácticamente cero (outputs/tablas/validacion_parcial.csv). El miedo no se parece a la cifra oculta. Fuente: outputs/tablas/validaciones.csv (IC por bootstrap de 2.000 réplicas).</t>
   </si>
   <si>
     <t>Qué explica sentir insegura la zona. Efectos marginales promedio en puntos porcentuales (pp) con IC 95 %.</t>
@@ -1994,61 +1997,61 @@
     <t>Bogotá 2025 = 7,937,898 habitantes (suma de localidades, cabecera + rural)</t>
   </si>
   <si>
+    <t>Bienal 2025</t>
+  </si>
+  <si>
+    <t>hoja 'datos': 5860 personas × 537 variables</t>
+  </si>
+  <si>
+    <t>universo</t>
+  </si>
+  <si>
+    <t>se conservan adultos (18+): 5639 de 5860; el modelo usa las 19 localidades urbanas</t>
+  </si>
+  <si>
+    <t>recodificación</t>
+  </si>
+  <si>
+    <t>escalas 1-4/1-5 → 1 si 'malo/muy malo' o 'insegura/muy insegura'; 'no sabe' queda vacío</t>
+  </si>
+  <si>
+    <t>peso</t>
+  </si>
+  <si>
+    <t>factor de expansión FACTOR: suma 6,308,418 adultos urbanos representados</t>
+  </si>
+  <si>
+    <t>EMV 2024</t>
+  </si>
+  <si>
+    <t>3624 encuestas nacionales; 1824 en Bogotá</t>
+  </si>
+  <si>
+    <t>localidad recuperada del tablero oficial (cruce por id de registro); sin localidad: 0</t>
+  </si>
+  <si>
+    <t>UAESP alumbrado</t>
+  </si>
+  <si>
+    <t>vigencia</t>
+  </si>
+  <si>
+    <t>último corte publicado en el portal: agosto de 2019, agregado por localidad</t>
+  </si>
+  <si>
+    <t>SCJ incidentes UPZ</t>
+  </si>
+  <si>
+    <t>geometría</t>
+  </si>
+  <si>
+    <t>117 UPZ con polígono simplificado (~20 m) en WGS84</t>
+  </si>
+  <si>
     <t>SDP población UPZ</t>
   </si>
   <si>
     <t>3472 filas (unidad × año × área); 36 columnas sexo×edad simple</t>
-  </si>
-  <si>
-    <t>Bienal 2025</t>
-  </si>
-  <si>
-    <t>hoja 'datos': 5860 personas × 537 variables</t>
-  </si>
-  <si>
-    <t>universo</t>
-  </si>
-  <si>
-    <t>se conservan adultos (18+): 5639 de 5860; el modelo usa las 19 localidades urbanas</t>
-  </si>
-  <si>
-    <t>recodificación</t>
-  </si>
-  <si>
-    <t>escalas 1-4/1-5 → 1 si 'malo/muy malo' o 'insegura/muy insegura'; 'no sabe' queda vacío</t>
-  </si>
-  <si>
-    <t>peso</t>
-  </si>
-  <si>
-    <t>factor de expansión FACTOR: suma 6,308,418 adultos urbanos representados</t>
-  </si>
-  <si>
-    <t>EMV 2024</t>
-  </si>
-  <si>
-    <t>3624 encuestas nacionales; 1824 en Bogotá</t>
-  </si>
-  <si>
-    <t>localidad recuperada del tablero oficial (cruce por id de registro); sin localidad: 0</t>
-  </si>
-  <si>
-    <t>UAESP alumbrado</t>
-  </si>
-  <si>
-    <t>vigencia</t>
-  </si>
-  <si>
-    <t>último corte publicado en el portal: agosto de 2019, agregado por localidad</t>
-  </si>
-  <si>
-    <t>SCJ incidentes UPZ</t>
-  </si>
-  <si>
-    <t>geometría</t>
-  </si>
-  <si>
-    <t>117 UPZ con polígono simplificado (~20 m) en WGS84</t>
   </si>
   <si>
     <t>Integración</t>
@@ -2097,7 +2100,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="13">
+  <numFmts count="14">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="\+0.00;&quot;−&quot;0.00;0.00"/>
@@ -2109,8 +2112,9 @@
     <numFmt numFmtId="172" formatCode="\+0.0%;&quot;−&quot;0.0%;0.0%"/>
     <numFmt numFmtId="173" formatCode="0.0"/>
     <numFmt numFmtId="174" formatCode="\+0.0;&quot;−&quot;0.0;0.0"/>
-    <numFmt numFmtId="175" formatCode="\+0.000;&quot;−&quot;0.000"/>
-    <numFmt numFmtId="176" formatCode="&quot;a  &quot;\+0.00;&quot;a  −&quot;0.00"/>
+    <numFmt numFmtId="175" formatCode="&quot;ρ = &quot;0.00;&quot;ρ = −&quot;0.00"/>
+    <numFmt numFmtId="176" formatCode="\+0.000;&quot;−&quot;0.000"/>
+    <numFmt numFmtId="177" formatCode="&quot;a  &quot;\+0.00;&quot;a  −&quot;0.00"/>
   </numFmts>
   <fonts count="49" x14ac:knownFonts="1">
     <font>
@@ -2863,7 +2867,7 @@
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="176" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2901,7 +2905,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="175" fontId="36" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="36" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2917,7 +2921,7 @@
       <alignment indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="36" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="36" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3134,7 +3138,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-5DB6-4C78-A040-3511C50AE800}"/>
+                <c16:uniqueId val="{00000001-9F2F-451F-BC00-06E6E6308354}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3153,7 +3157,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-5DB6-4C78-A040-3511C50AE800}"/>
+                <c16:uniqueId val="{00000003-9F2F-451F-BC00-06E6E6308354}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3172,7 +3176,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-5DB6-4C78-A040-3511C50AE800}"/>
+                <c16:uniqueId val="{00000005-9F2F-451F-BC00-06E6E6308354}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3191,7 +3195,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-5DB6-4C78-A040-3511C50AE800}"/>
+                <c16:uniqueId val="{00000007-9F2F-451F-BC00-06E6E6308354}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3210,7 +3214,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-5DB6-4C78-A040-3511C50AE800}"/>
+                <c16:uniqueId val="{00000009-9F2F-451F-BC00-06E6E6308354}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3229,7 +3233,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-5DB6-4C78-A040-3511C50AE800}"/>
+                <c16:uniqueId val="{0000000B-9F2F-451F-BC00-06E6E6308354}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3248,7 +3252,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-5DB6-4C78-A040-3511C50AE800}"/>
+                <c16:uniqueId val="{0000000D-9F2F-451F-BC00-06E6E6308354}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3267,7 +3271,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-5DB6-4C78-A040-3511C50AE800}"/>
+                <c16:uniqueId val="{0000000F-9F2F-451F-BC00-06E6E6308354}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3286,7 +3290,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000011-5DB6-4C78-A040-3511C50AE800}"/>
+                <c16:uniqueId val="{00000011-9F2F-451F-BC00-06E6E6308354}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3305,7 +3309,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000013-5DB6-4C78-A040-3511C50AE800}"/>
+                <c16:uniqueId val="{00000013-9F2F-451F-BC00-06E6E6308354}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3324,7 +3328,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000015-5DB6-4C78-A040-3511C50AE800}"/>
+                <c16:uniqueId val="{00000015-9F2F-451F-BC00-06E6E6308354}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3343,7 +3347,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000017-5DB6-4C78-A040-3511C50AE800}"/>
+                <c16:uniqueId val="{00000017-9F2F-451F-BC00-06E6E6308354}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3362,7 +3366,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000019-5DB6-4C78-A040-3511C50AE800}"/>
+                <c16:uniqueId val="{00000019-9F2F-451F-BC00-06E6E6308354}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3381,7 +3385,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001B-5DB6-4C78-A040-3511C50AE800}"/>
+                <c16:uniqueId val="{0000001B-9F2F-451F-BC00-06E6E6308354}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3400,7 +3404,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001D-5DB6-4C78-A040-3511C50AE800}"/>
+                <c16:uniqueId val="{0000001D-9F2F-451F-BC00-06E6E6308354}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3419,7 +3423,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000001F-5DB6-4C78-A040-3511C50AE800}"/>
+                <c16:uniqueId val="{0000001F-9F2F-451F-BC00-06E6E6308354}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3438,7 +3442,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000021-5DB6-4C78-A040-3511C50AE800}"/>
+                <c16:uniqueId val="{00000021-9F2F-451F-BC00-06E6E6308354}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3457,7 +3461,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000023-5DB6-4C78-A040-3511C50AE800}"/>
+                <c16:uniqueId val="{00000023-9F2F-451F-BC00-06E6E6308354}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3476,7 +3480,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000025-5DB6-4C78-A040-3511C50AE800}"/>
+                <c16:uniqueId val="{00000025-9F2F-451F-BC00-06E6E6308354}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -3758,7 +3762,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000026-5DB6-4C78-A040-3511C50AE800}"/>
+              <c16:uniqueId val="{00000026-9F2F-451F-BC00-06E6E6308354}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4204,7 +4208,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A923-438F-B589-71092CB8A60E}"/>
+              <c16:uniqueId val="{00000000-3C5D-4F3E-BC62-DCC104FD5206}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4501,7 +4505,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-BE0B-4A62-8213-37EB38600B14}"/>
+              <c16:uniqueId val="{00000000-BAA0-48F7-A792-62FB5918FEAB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4660,7 +4664,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-068A-4790-A6C3-759EA147DEB0}"/>
+                <c16:uniqueId val="{00000001-98B1-45A1-B3A8-C363694940CF}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4679,7 +4683,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-068A-4790-A6C3-759EA147DEB0}"/>
+                <c16:uniqueId val="{00000003-98B1-45A1-B3A8-C363694940CF}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4698,7 +4702,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-068A-4790-A6C3-759EA147DEB0}"/>
+                <c16:uniqueId val="{00000005-98B1-45A1-B3A8-C363694940CF}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4717,7 +4721,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-068A-4790-A6C3-759EA147DEB0}"/>
+                <c16:uniqueId val="{00000007-98B1-45A1-B3A8-C363694940CF}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4736,7 +4740,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-068A-4790-A6C3-759EA147DEB0}"/>
+                <c16:uniqueId val="{00000009-98B1-45A1-B3A8-C363694940CF}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4755,7 +4759,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-068A-4790-A6C3-759EA147DEB0}"/>
+                <c16:uniqueId val="{0000000B-98B1-45A1-B3A8-C363694940CF}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4774,7 +4778,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000D-068A-4790-A6C3-759EA147DEB0}"/>
+                <c16:uniqueId val="{0000000D-98B1-45A1-B3A8-C363694940CF}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4793,7 +4797,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000F-068A-4790-A6C3-759EA147DEB0}"/>
+                <c16:uniqueId val="{0000000F-98B1-45A1-B3A8-C363694940CF}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4812,7 +4816,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000011-068A-4790-A6C3-759EA147DEB0}"/>
+                <c16:uniqueId val="{00000011-98B1-45A1-B3A8-C363694940CF}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4831,7 +4835,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000013-068A-4790-A6C3-759EA147DEB0}"/>
+                <c16:uniqueId val="{00000013-98B1-45A1-B3A8-C363694940CF}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4850,7 +4854,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000015-068A-4790-A6C3-759EA147DEB0}"/>
+                <c16:uniqueId val="{00000015-98B1-45A1-B3A8-C363694940CF}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -4869,7 +4873,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000017-068A-4790-A6C3-759EA147DEB0}"/>
+                <c16:uniqueId val="{00000017-98B1-45A1-B3A8-C363694940CF}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5067,7 +5071,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000018-068A-4790-A6C3-759EA147DEB0}"/>
+              <c16:uniqueId val="{00000018-98B1-45A1-B3A8-C363694940CF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5230,7 +5234,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-4F3F-4A46-BDE3-6F7BB0601FB1}"/>
+                <c16:uniqueId val="{00000001-BA72-422A-AA87-A28EB6F025C5}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5249,7 +5253,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-4F3F-4A46-BDE3-6F7BB0601FB1}"/>
+                <c16:uniqueId val="{00000003-BA72-422A-AA87-A28EB6F025C5}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5268,7 +5272,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000005-4F3F-4A46-BDE3-6F7BB0601FB1}"/>
+                <c16:uniqueId val="{00000005-BA72-422A-AA87-A28EB6F025C5}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5287,7 +5291,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000007-4F3F-4A46-BDE3-6F7BB0601FB1}"/>
+                <c16:uniqueId val="{00000007-BA72-422A-AA87-A28EB6F025C5}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5306,7 +5310,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000009-4F3F-4A46-BDE3-6F7BB0601FB1}"/>
+                <c16:uniqueId val="{00000009-BA72-422A-AA87-A28EB6F025C5}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5325,7 +5329,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{0000000B-4F3F-4A46-BDE3-6F7BB0601FB1}"/>
+                <c16:uniqueId val="{0000000B-BA72-422A-AA87-A28EB6F025C5}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -5421,7 +5425,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{0000000C-4F3F-4A46-BDE3-6F7BB0601FB1}"/>
+              <c16:uniqueId val="{0000000C-BA72-422A-AA87-A28EB6F025C5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5669,7 +5673,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1E7B-4BCD-BCAD-21AD63A65162}"/>
+              <c16:uniqueId val="{00000000-ACF4-461B-BC66-C71C4E6D84F6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5782,7 +5786,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-1E7B-4BCD-BCAD-21AD63A65162}"/>
+              <c16:uniqueId val="{00000001-ACF4-461B-BC66-C71C4E6D84F6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6055,7 +6059,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6E39-48E1-B0B6-4294AAC37960}"/>
+              <c16:uniqueId val="{00000000-48DE-40E7-92FA-2F5005768EBC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6302,7 +6306,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A59F-46A1-8469-E9E033B9AC7E}"/>
+              <c16:uniqueId val="{00000000-E85D-4959-A215-74AA10F68DA2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6417,7 +6421,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-A59F-46A1-8469-E9E033B9AC7E}"/>
+              <c16:uniqueId val="{00000001-E85D-4959-A215-74AA10F68DA2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6532,7 +6536,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-A59F-46A1-8469-E9E033B9AC7E}"/>
+              <c16:uniqueId val="{00000002-E85D-4959-A215-74AA10F68DA2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6877,7 +6881,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8DEA-4C70-B4AF-5AA9F86ABA01}"/>
+              <c16:uniqueId val="{00000000-B39A-4880-8586-C8432878F7D5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8089,7 +8093,7 @@
     </row>
     <row r="3" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="16" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="4" spans="2:9" ht="3" customHeight="1" x14ac:dyDescent="0.25">
@@ -8105,51 +8109,51 @@
     <row r="5" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="20" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="I6" s="20" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="75" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C7" s="76" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D7" s="77" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E7" s="75" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F7" s="75" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G7" s="75" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H7" s="75" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I7" s="75" t="s">
         <v>19</v>
@@ -8157,77 +8161,77 @@
     </row>
     <row r="8" spans="2:9" ht="46.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="75" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C8" s="76" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D8" s="77" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E8" s="75" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F8" s="75" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G8" s="75" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H8" s="75" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I8" s="75" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="75" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C9" s="76" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D9" s="77" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E9" s="75" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F9" s="75" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G9" s="75" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H9" s="75" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I9" s="75" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="10" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="75" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C10" s="76" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D10" s="77" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E10" s="75" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F10" s="75" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G10" s="75" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H10" s="75" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I10" s="75" t="s">
         <v>19</v>
@@ -8235,103 +8239,103 @@
     </row>
     <row r="11" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="75" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C11" s="76" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D11" s="77" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E11" s="75" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F11" s="75" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G11" s="75" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H11" s="75" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I11" s="75" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="12" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="75" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C12" s="76" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D12" s="77" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E12" s="75" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F12" s="75" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G12" s="75" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H12" s="75" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I12" s="75" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="13" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="75" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C13" s="76" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D13" s="77" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E13" s="75" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F13" s="75" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G13" s="75" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H13" s="75" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I13" s="75" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="14" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="75" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C14" s="76" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D14" s="77" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E14" s="75" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F14" s="75" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G14" s="75" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H14" s="75" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I14" s="75" t="s">
         <v>19</v>
@@ -8339,181 +8343,181 @@
     </row>
     <row r="15" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="75" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C15" s="76" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D15" s="77" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E15" s="75" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F15" s="75" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G15" s="75" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H15" s="75" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I15" s="75" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="16" spans="2:9" ht="46.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="75" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C16" s="76" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D16" s="77" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E16" s="75" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F16" s="75" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G16" s="75" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H16" s="75" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I16" s="75" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="46.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="75" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C17" s="76" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D17" s="77" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E17" s="75" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F17" s="75" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G17" s="75" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H17" s="75" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I17" s="75" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="18" spans="2:9" ht="46.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="75" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C18" s="76" t="s">
+        <v>418</v>
+      </c>
+      <c r="D18" s="77" t="s">
+        <v>281</v>
+      </c>
+      <c r="E18" s="75" t="s">
+        <v>419</v>
+      </c>
+      <c r="F18" s="75" t="s">
+        <v>399</v>
+      </c>
+      <c r="G18" s="75" t="s">
+        <v>412</v>
+      </c>
+      <c r="H18" s="75" t="s">
+        <v>307</v>
+      </c>
+      <c r="I18" s="75" t="s">
         <v>417</v>
-      </c>
-      <c r="D18" s="77" t="s">
-        <v>280</v>
-      </c>
-      <c r="E18" s="75" t="s">
-        <v>418</v>
-      </c>
-      <c r="F18" s="75" t="s">
-        <v>398</v>
-      </c>
-      <c r="G18" s="75" t="s">
-        <v>411</v>
-      </c>
-      <c r="H18" s="75" t="s">
-        <v>306</v>
-      </c>
-      <c r="I18" s="75" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="19" spans="2:9" ht="46.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="75" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C19" s="76" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D19" s="77" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E19" s="75" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F19" s="75" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G19" s="75" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H19" s="75" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I19" s="75" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="46.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="75" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C20" s="76" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D20" s="77" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E20" s="75" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F20" s="75" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G20" s="75" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H20" s="75" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I20" s="75" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="21" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="75" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C21" s="76" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D21" s="77" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E21" s="75" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F21" s="75" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G21" s="75" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H21" s="75" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I21" s="75" t="s">
         <v>19</v>
@@ -8521,51 +8525,51 @@
     </row>
     <row r="22" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="75" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C22" s="76" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D22" s="77" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E22" s="75" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F22" s="75" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G22" s="75" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H22" s="75" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I22" s="75" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="23" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="75" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C23" s="76" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D23" s="77" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E23" s="75" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F23" s="75" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G23" s="75" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H23" s="75" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I23" s="75" t="s">
         <v>19</v>
@@ -8573,51 +8577,51 @@
     </row>
     <row r="24" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="75" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C24" s="76" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D24" s="77" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E24" s="75" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F24" s="75" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G24" s="75" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H24" s="75" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I24" s="75" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="25" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="75" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C25" s="76" t="s">
+        <v>442</v>
+      </c>
+      <c r="D25" s="77" t="s">
+        <v>443</v>
+      </c>
+      <c r="E25" s="75" t="s">
+        <v>444</v>
+      </c>
+      <c r="F25" s="75" t="s">
+        <v>425</v>
+      </c>
+      <c r="G25" s="75" t="s">
         <v>441</v>
       </c>
-      <c r="D25" s="77" t="s">
-        <v>442</v>
-      </c>
-      <c r="E25" s="75" t="s">
-        <v>443</v>
-      </c>
-      <c r="F25" s="75" t="s">
-        <v>424</v>
-      </c>
-      <c r="G25" s="75" t="s">
-        <v>440</v>
-      </c>
       <c r="H25" s="75" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I25" s="75" t="s">
         <v>19</v>
@@ -8625,25 +8629,25 @@
     </row>
     <row r="26" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="75" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C26" s="76" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D26" s="77" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E26" s="75" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F26" s="75" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G26" s="75" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H26" s="75" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I26" s="75" t="s">
         <v>19</v>
@@ -8651,25 +8655,25 @@
     </row>
     <row r="27" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="75" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C27" s="76" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D27" s="77" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E27" s="75" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F27" s="75" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G27" s="75" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H27" s="75" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="I27" s="75" t="s">
         <v>19</v>
@@ -8677,51 +8681,51 @@
     </row>
     <row r="28" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="75" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C28" s="76" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D28" s="77" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E28" s="75" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F28" s="75" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="G28" s="75" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H28" s="75" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="I28" s="75" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="29" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="75" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C29" s="76" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D29" s="77" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E29" s="75" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F29" s="75" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G29" s="75" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H29" s="75" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="I29" s="75" t="s">
         <v>19</v>
@@ -8729,51 +8733,51 @@
     </row>
     <row r="30" spans="2:9" ht="46.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="75" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C30" s="76" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D30" s="77" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E30" s="75" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F30" s="75" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="G30" s="75" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H30" s="75" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="I30" s="75" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="31" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="75" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C31" s="76" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D31" s="77" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E31" s="75" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F31" s="75" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G31" s="75" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H31" s="75" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="I31" s="75" t="s">
         <v>29</v>
@@ -8781,103 +8785,103 @@
     </row>
     <row r="32" spans="2:9" ht="59.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="75" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C32" s="76" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D32" s="77" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E32" s="75" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F32" s="75" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G32" s="75" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H32" s="75" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="I32" s="75" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="59.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="75" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C33" s="76" t="s">
+        <v>486</v>
+      </c>
+      <c r="D33" s="77" t="s">
+        <v>219</v>
+      </c>
+      <c r="E33" s="75" t="s">
+        <v>487</v>
+      </c>
+      <c r="F33" s="75" t="s">
+        <v>488</v>
+      </c>
+      <c r="G33" s="75" t="s">
+        <v>483</v>
+      </c>
+      <c r="H33" s="75" t="s">
+        <v>484</v>
+      </c>
+      <c r="I33" s="75" t="s">
         <v>485</v>
-      </c>
-      <c r="D33" s="77" t="s">
-        <v>218</v>
-      </c>
-      <c r="E33" s="75" t="s">
-        <v>486</v>
-      </c>
-      <c r="F33" s="75" t="s">
-        <v>487</v>
-      </c>
-      <c r="G33" s="75" t="s">
-        <v>482</v>
-      </c>
-      <c r="H33" s="75" t="s">
-        <v>483</v>
-      </c>
-      <c r="I33" s="75" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="34" spans="2:9" ht="59.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="75" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C34" s="76" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D34" s="77" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E34" s="75" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F34" s="75" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="G34" s="75" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H34" s="75" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="I34" s="75" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="35" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="75" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C35" s="76" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D35" s="77" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E35" s="75" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F35" s="75" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G35" s="75" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H35" s="75" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I35" s="75" t="s">
         <v>25</v>
@@ -8885,25 +8889,25 @@
     </row>
     <row r="36" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="75" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C36" s="76" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D36" s="77" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E36" s="75" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F36" s="75" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="G36" s="75" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H36" s="75" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I36" s="75" t="s">
         <v>25</v>
@@ -8911,25 +8915,25 @@
     </row>
     <row r="37" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="75" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C37" s="76" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D37" s="77" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E37" s="75" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F37" s="75" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G37" s="75" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H37" s="75" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I37" s="75" t="s">
         <v>25</v>
@@ -8937,25 +8941,25 @@
     </row>
     <row r="38" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="75" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C38" s="76" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D38" s="77" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E38" s="75" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F38" s="75" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G38" s="75" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H38" s="75" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="I38" s="75" t="s">
         <v>25</v>
@@ -8963,25 +8967,25 @@
     </row>
     <row r="39" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="75" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C39" s="76" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D39" s="77" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E39" s="75" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F39" s="75" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G39" s="75" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H39" s="75" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I39" s="75" t="s">
         <v>25</v>
@@ -8989,25 +8993,25 @@
     </row>
     <row r="40" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="75" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C40" s="76" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D40" s="77" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E40" s="75" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F40" s="75" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G40" s="75" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H40" s="75" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I40" s="75" t="s">
         <v>25</v>
@@ -9015,25 +9019,25 @@
     </row>
     <row r="41" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="75" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C41" s="76" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D41" s="77" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E41" s="75" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F41" s="75" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G41" s="75" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H41" s="75" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I41" s="75" t="s">
         <v>25</v>
@@ -9041,25 +9045,25 @@
     </row>
     <row r="42" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="75" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C42" s="76" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D42" s="77" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E42" s="75" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F42" s="75" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G42" s="75" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H42" s="75" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I42" s="75" t="s">
         <v>25</v>
@@ -9067,155 +9071,155 @@
     </row>
     <row r="43" spans="2:9" ht="59.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="75" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C43" s="76" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D43" s="77" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E43" s="75" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F43" s="75" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G43" s="75" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H43" s="75" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I43" s="75" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="44" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="75" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C44" s="76" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D44" s="77" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E44" s="75" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F44" s="75" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G44" s="75" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H44" s="75" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I44" s="75" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="45" spans="2:9" ht="46.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="75" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C45" s="76" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D45" s="77" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E45" s="75" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F45" s="75" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="G45" s="75" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H45" s="75" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I45" s="75" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="46" spans="2:9" ht="46.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="75" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C46" s="76" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D46" s="77" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E46" s="75" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F46" s="75" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="G46" s="75" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H46" s="75" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I46" s="75" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="47" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="75" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C47" s="76" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D47" s="77" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E47" s="75" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F47" s="75" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="G47" s="75" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H47" s="75" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I47" s="75" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="48" spans="2:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="75" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C48" s="76" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D48" s="77" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E48" s="75" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F48" s="75" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="G48" s="75" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H48" s="75" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I48" s="75" t="s">
         <v>25</v>
@@ -9223,54 +9227,54 @@
     </row>
     <row r="49" spans="2:9" ht="46.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="75" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C49" s="76" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D49" s="77" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E49" s="75" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F49" s="75" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="G49" s="75" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H49" s="75" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="I49" s="75" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="50" spans="2:9" ht="46.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="75" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C50" s="76" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D50" s="77" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E50" s="75" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F50" s="75" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G50" s="75" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H50" s="75" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I50" s="75" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
   </sheetData>
@@ -9329,7 +9333,7 @@
     </row>
     <row r="3" spans="2:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="16" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="3" customHeight="1" x14ac:dyDescent="0.25">
@@ -9343,227 +9347,227 @@
     <row r="5" spans="2:7" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="20" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="7" spans="2:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="75" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C7" s="75" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D7" s="75" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E7" s="78" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F7" s="79" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="G7" s="80" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="8" spans="2:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="75" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C8" s="75" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D8" s="75" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E8" s="78" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="F8" s="79" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="G8" s="80" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="75" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C9" s="75" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D9" s="75" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E9" s="78" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="F9" s="79" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="G9" s="80" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="10" spans="2:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="75" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C10" s="75" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D10" s="75" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E10" s="78" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="F10" s="79" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="G10" s="80" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="11" spans="2:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="75" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C11" s="75" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D11" s="75" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E11" s="78" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F11" s="79" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="G11" s="80" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="12" spans="2:7" ht="44.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="75" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C12" s="75" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D12" s="75" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E12" s="78" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F12" s="79" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="G12" s="80" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="13" spans="2:7" ht="44.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="75" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C13" s="75" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D13" s="75" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E13" s="78" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F13" s="79" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="G13" s="80" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="75" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C14" s="75" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D14" s="75" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="E14" s="78" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F14" s="79" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="G14" s="80" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="15" spans="2:7" ht="46.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="75" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C15" s="75" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D15" s="75" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E15" s="78" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F15" s="79" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="G15" s="80" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="46.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="75" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C16" s="75" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D16" s="75" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E16" s="78" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F16" s="79" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="G16" s="80" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="130" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C18" s="84"/>
       <c r="D18" s="84"/>
@@ -9639,12 +9643,12 @@
     </row>
     <row r="2" spans="2:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="15" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="3" spans="2:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="16" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="4" spans="2:5" ht="3" customHeight="1" x14ac:dyDescent="0.25">
@@ -9656,16 +9660,16 @@
     <row r="5" spans="2:5" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:5" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="20" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="7" spans="2:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
@@ -9673,13 +9677,13 @@
         <v>1</v>
       </c>
       <c r="C7" s="57" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E7" s="81" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="8" spans="2:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
@@ -9687,13 +9691,13 @@
         <v>2</v>
       </c>
       <c r="C8" s="57" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E8" s="81" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="9" spans="2:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
@@ -9701,13 +9705,13 @@
         <v>3</v>
       </c>
       <c r="C9" s="57" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E9" s="81" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="10" spans="2:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
@@ -9715,13 +9719,13 @@
         <v>4</v>
       </c>
       <c r="C10" s="57" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E10" s="81" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="11" spans="2:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
@@ -9729,13 +9733,13 @@
         <v>5</v>
       </c>
       <c r="C11" s="57" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E11" s="81" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="12" spans="2:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
@@ -9743,13 +9747,13 @@
         <v>6</v>
       </c>
       <c r="C12" s="57" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="E12" s="81" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="13" spans="2:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
@@ -9757,13 +9761,13 @@
         <v>7</v>
       </c>
       <c r="C13" s="57" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E13" s="81" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="14" spans="2:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
@@ -9771,13 +9775,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="57" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E14" s="81" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="15" spans="2:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
@@ -9785,13 +9789,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="57" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E15" s="81" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="16" spans="2:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
@@ -9799,13 +9803,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="57" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>612</v>
+        <v>630</v>
       </c>
       <c r="E16" s="81" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
@@ -9813,13 +9817,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="57" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E17" s="81" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
@@ -9827,13 +9831,13 @@
         <v>12</v>
       </c>
       <c r="C18" s="57" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="E18" s="81" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
@@ -9841,13 +9845,13 @@
         <v>13</v>
       </c>
       <c r="C19" s="57" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>635</v>
+        <v>613</v>
       </c>
       <c r="E19" s="81" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
@@ -9855,10 +9859,10 @@
         <v>14</v>
       </c>
       <c r="C20" s="57" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="E20" s="81" t="s">
         <v>638</v>
@@ -9869,13 +9873,13 @@
         <v>15</v>
       </c>
       <c r="C21" s="57" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>616</v>
+        <v>640</v>
       </c>
       <c r="E21" s="81" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="22" spans="2:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
@@ -9883,13 +9887,13 @@
         <v>16</v>
       </c>
       <c r="C22" s="57" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>641</v>
+        <v>615</v>
       </c>
       <c r="E22" s="81" t="s">
-        <v>642</v>
+        <v>623</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
@@ -9897,13 +9901,13 @@
         <v>17</v>
       </c>
       <c r="C23" s="57" t="s">
+        <v>642</v>
+      </c>
+      <c r="D23" s="22" t="s">
         <v>643</v>
       </c>
-      <c r="D23" s="22" t="s">
-        <v>614</v>
-      </c>
       <c r="E23" s="81" t="s">
-        <v>622</v>
+        <v>644</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
@@ -9911,13 +9915,13 @@
         <v>18</v>
       </c>
       <c r="C24" s="57" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>644</v>
+        <v>613</v>
       </c>
       <c r="E24" s="81" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="25" spans="2:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
@@ -9925,13 +9929,13 @@
         <v>19</v>
       </c>
       <c r="C25" s="57" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D25" s="22" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E25" s="81" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="20.85" customHeight="1" x14ac:dyDescent="0.25">
@@ -9939,18 +9943,18 @@
         <v>20</v>
       </c>
       <c r="C26" s="57" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E26" s="81" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="130" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C28" s="84"/>
       <c r="D28" s="84"/>
@@ -10010,12 +10014,12 @@
     </row>
     <row r="2" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="15" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="16" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="4" spans="2:9" ht="3" customHeight="1" x14ac:dyDescent="0.25">
@@ -10031,7 +10035,7 @@
     <row r="5" spans="2:9" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="2:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="20" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C7" s="20" t="s">
         <v>98</v>
@@ -10040,30 +10044,30 @@
         <v>85</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="I7" s="20" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="8" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="57" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C8" s="56">
         <v>0</v>
       </c>
       <c r="D8" s="57" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E8" s="82">
         <v>0.48389447949095249</v>
@@ -10083,7 +10087,7 @@
     </row>
     <row r="9" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="22" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C9" s="21">
         <v>1</v>
@@ -10109,7 +10113,7 @@
     </row>
     <row r="10" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="22" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C10" s="21">
         <v>2</v>
@@ -10135,7 +10139,7 @@
     </row>
     <row r="11" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="22" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C11" s="21">
         <v>3</v>
@@ -10161,7 +10165,7 @@
     </row>
     <row r="12" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="22" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C12" s="21">
         <v>4</v>
@@ -10187,7 +10191,7 @@
     </row>
     <row r="13" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="22" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C13" s="21">
         <v>5</v>
@@ -10213,7 +10217,7 @@
     </row>
     <row r="14" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="22" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C14" s="21">
         <v>6</v>
@@ -10239,7 +10243,7 @@
     </row>
     <row r="15" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="22" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C15" s="21">
         <v>7</v>
@@ -10265,7 +10269,7 @@
     </row>
     <row r="16" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="22" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C16" s="21">
         <v>8</v>
@@ -10291,7 +10295,7 @@
     </row>
     <row r="17" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="22" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C17" s="21">
         <v>9</v>
@@ -10317,7 +10321,7 @@
     </row>
     <row r="18" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="22" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C18" s="21">
         <v>10</v>
@@ -10343,7 +10347,7 @@
     </row>
     <row r="19" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="22" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C19" s="21">
         <v>11</v>
@@ -10369,7 +10373,7 @@
     </row>
     <row r="20" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="22" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C20" s="21">
         <v>12</v>
@@ -10395,7 +10399,7 @@
     </row>
     <row r="21" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="22" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C21" s="21">
         <v>13</v>
@@ -10421,7 +10425,7 @@
     </row>
     <row r="22" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="22" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C22" s="21">
         <v>14</v>
@@ -10447,7 +10451,7 @@
     </row>
     <row r="23" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="22" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C23" s="21">
         <v>15</v>
@@ -10473,7 +10477,7 @@
     </row>
     <row r="24" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="22" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C24" s="21">
         <v>16</v>
@@ -10499,7 +10503,7 @@
     </row>
     <row r="25" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="22" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C25" s="21">
         <v>17</v>
@@ -10525,7 +10529,7 @@
     </row>
     <row r="26" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="22" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C26" s="21">
         <v>18</v>
@@ -10551,7 +10555,7 @@
     </row>
     <row r="27" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="22" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C27" s="21">
         <v>19</v>
@@ -10577,13 +10581,13 @@
     </row>
     <row r="28" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="57" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C28" s="56">
         <v>0</v>
       </c>
       <c r="D28" s="57" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E28" s="82">
         <v>0.47603691541823467</v>
@@ -10603,7 +10607,7 @@
     </row>
     <row r="29" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="22" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C29" s="21">
         <v>1</v>
@@ -10629,7 +10633,7 @@
     </row>
     <row r="30" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="22" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C30" s="21">
         <v>2</v>
@@ -10655,7 +10659,7 @@
     </row>
     <row r="31" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="22" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C31" s="21">
         <v>3</v>
@@ -10681,7 +10685,7 @@
     </row>
     <row r="32" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="22" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C32" s="21">
         <v>4</v>
@@ -10707,7 +10711,7 @@
     </row>
     <row r="33" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="22" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C33" s="21">
         <v>5</v>
@@ -10733,7 +10737,7 @@
     </row>
     <row r="34" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="22" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C34" s="21">
         <v>6</v>
@@ -10759,7 +10763,7 @@
     </row>
     <row r="35" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="22" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C35" s="21">
         <v>7</v>
@@ -10785,7 +10789,7 @@
     </row>
     <row r="36" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="22" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C36" s="21">
         <v>8</v>
@@ -10811,7 +10815,7 @@
     </row>
     <row r="37" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="22" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C37" s="21">
         <v>9</v>
@@ -10837,7 +10841,7 @@
     </row>
     <row r="38" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="22" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C38" s="21">
         <v>10</v>
@@ -10863,7 +10867,7 @@
     </row>
     <row r="39" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="22" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C39" s="21">
         <v>11</v>
@@ -10889,7 +10893,7 @@
     </row>
     <row r="40" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="22" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C40" s="21">
         <v>12</v>
@@ -10915,7 +10919,7 @@
     </row>
     <row r="41" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="22" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C41" s="21">
         <v>13</v>
@@ -10941,7 +10945,7 @@
     </row>
     <row r="42" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="22" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C42" s="21">
         <v>14</v>
@@ -10967,7 +10971,7 @@
     </row>
     <row r="43" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="22" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C43" s="21">
         <v>15</v>
@@ -10993,7 +10997,7 @@
     </row>
     <row r="44" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="22" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C44" s="21">
         <v>16</v>
@@ -11019,7 +11023,7 @@
     </row>
     <row r="45" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="22" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C45" s="21">
         <v>17</v>
@@ -11045,7 +11049,7 @@
     </row>
     <row r="46" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="22" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C46" s="21">
         <v>18</v>
@@ -11071,7 +11075,7 @@
     </row>
     <row r="47" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="22" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C47" s="21">
         <v>19</v>
@@ -11097,13 +11101,13 @@
     </row>
     <row r="48" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="57" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C48" s="56">
         <v>0</v>
       </c>
       <c r="D48" s="57" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E48" s="82">
         <v>0.49263396747665222</v>
@@ -11123,7 +11127,7 @@
     </row>
     <row r="49" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C49" s="21">
         <v>1</v>
@@ -11149,7 +11153,7 @@
     </row>
     <row r="50" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C50" s="21">
         <v>2</v>
@@ -11175,7 +11179,7 @@
     </row>
     <row r="51" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C51" s="21">
         <v>3</v>
@@ -11201,7 +11205,7 @@
     </row>
     <row r="52" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C52" s="21">
         <v>4</v>
@@ -11227,7 +11231,7 @@
     </row>
     <row r="53" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C53" s="21">
         <v>5</v>
@@ -11253,7 +11257,7 @@
     </row>
     <row r="54" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C54" s="21">
         <v>6</v>
@@ -11279,7 +11283,7 @@
     </row>
     <row r="55" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C55" s="21">
         <v>7</v>
@@ -11305,7 +11309,7 @@
     </row>
     <row r="56" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C56" s="21">
         <v>8</v>
@@ -11331,7 +11335,7 @@
     </row>
     <row r="57" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C57" s="21">
         <v>9</v>
@@ -11357,7 +11361,7 @@
     </row>
     <row r="58" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C58" s="21">
         <v>10</v>
@@ -11383,7 +11387,7 @@
     </row>
     <row r="59" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C59" s="21">
         <v>11</v>
@@ -11409,7 +11413,7 @@
     </row>
     <row r="60" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C60" s="21">
         <v>12</v>
@@ -11435,7 +11439,7 @@
     </row>
     <row r="61" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C61" s="21">
         <v>13</v>
@@ -11461,7 +11465,7 @@
     </row>
     <row r="62" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C62" s="21">
         <v>14</v>
@@ -11487,7 +11491,7 @@
     </row>
     <row r="63" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C63" s="21">
         <v>15</v>
@@ -11513,7 +11517,7 @@
     </row>
     <row r="64" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C64" s="21">
         <v>16</v>
@@ -11539,7 +11543,7 @@
     </row>
     <row r="65" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C65" s="21">
         <v>17</v>
@@ -11565,7 +11569,7 @@
     </row>
     <row r="66" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C66" s="21">
         <v>18</v>
@@ -11591,7 +11595,7 @@
     </row>
     <row r="67" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C67" s="21">
         <v>19</v>
@@ -11617,7 +11621,7 @@
     </row>
     <row r="69" spans="2:9" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="130" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C69" s="84"/>
       <c r="D69" s="84"/>
@@ -11848,8 +11852,7 @@
       <c r="G13" s="100"/>
       <c r="H13" s="100"/>
       <c r="J13" s="123">
-        <f>Cifra_oculta!$J$29</f>
-        <v>0.71578947368421053</v>
+        <v>-2.3E-2</v>
       </c>
       <c r="K13" s="100"/>
       <c r="L13" s="100"/>
@@ -15749,7 +15752,7 @@
     <tabColor rgb="FFAB0F24"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:R63"/>
+  <dimension ref="B1:R64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.42578125" customWidth="1"/>
@@ -17098,13 +17101,13 @@
         <v>0.73178269464115531</v>
       </c>
       <c r="L56" s="42">
-        <v>0.85374647708134788</v>
+        <v>0.83632307958989183</v>
       </c>
       <c r="M56" s="21">
         <v>19</v>
       </c>
       <c r="N56" s="21" t="str">
-        <f t="shared" ref="N56:N62" si="7">IF(L56&lt;0.05,"Sí","No")</f>
+        <f t="shared" ref="N56:N63" si="7">IF(L56&lt;0.05,"Sí","No")</f>
         <v>No</v>
       </c>
     </row>
@@ -17130,7 +17133,7 @@
         <v>0.35534598974510739</v>
       </c>
       <c r="L57" s="42">
-        <v>0.62185548205393804</v>
+        <v>0.7106919794902149</v>
       </c>
       <c r="M57" s="21">
         <v>19</v>
@@ -17162,7 +17165,7 @@
         <v>0.65238568732726732</v>
       </c>
       <c r="L58" s="42">
-        <v>0.85374647708134788</v>
+        <v>0.83632307958989183</v>
       </c>
       <c r="M58" s="21">
         <v>19</v>
@@ -17226,7 +17229,7 @@
         <v>0.30370908654883683</v>
       </c>
       <c r="L60" s="42">
-        <v>0.62185548205393804</v>
+        <v>0.7106919794902149</v>
       </c>
       <c r="M60" s="21">
         <v>19</v>
@@ -17258,7 +17261,7 @@
         <v>0.14724536947686551</v>
       </c>
       <c r="L61" s="42">
-        <v>0.51535879316902944</v>
+        <v>0.58898147790746225</v>
       </c>
       <c r="M61" s="21">
         <v>19</v>
@@ -17278,53 +17281,86 @@
       <c r="F62" s="135"/>
       <c r="G62" s="135"/>
       <c r="H62" s="28">
-        <v>0.71578947368421042</v>
+        <v>0.1614035087719298</v>
       </c>
       <c r="I62" s="28">
-        <v>0.4121535667984571</v>
+        <v>-0.31920908202390791</v>
       </c>
       <c r="J62" s="28">
-        <v>0.8762464016659518</v>
+        <v>0.58065157867716266</v>
       </c>
       <c r="K62" s="42">
-        <v>5.6846911390540003E-4</v>
+        <v>0.50917134274716958</v>
       </c>
       <c r="L62" s="42">
-        <v>3.9792837973378001E-3</v>
+        <v>0.81467414839547136</v>
       </c>
       <c r="M62" s="21">
         <v>19</v>
       </c>
       <c r="N62" s="21" t="str">
         <f t="shared" si="7"/>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="63" spans="2:15" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="134" t="s">
+        <v>206</v>
+      </c>
+      <c r="C63" s="135"/>
+      <c r="D63" s="135"/>
+      <c r="E63" s="135"/>
+      <c r="F63" s="135"/>
+      <c r="G63" s="135"/>
+      <c r="H63" s="28">
+        <v>0.71578947368421042</v>
+      </c>
+      <c r="I63" s="28">
+        <v>0.4121535667984571</v>
+      </c>
+      <c r="J63" s="28">
+        <v>0.8762464016659518</v>
+      </c>
+      <c r="K63" s="42">
+        <v>5.6846911390540003E-4</v>
+      </c>
+      <c r="L63" s="42">
+        <v>4.5477529112433E-3</v>
+      </c>
+      <c r="M63" s="21">
+        <v>19</v>
+      </c>
+      <c r="N63" s="21" t="str">
+        <f t="shared" si="7"/>
         <v>Sí</v>
       </c>
     </row>
-    <row r="63" spans="2:15" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="130" t="s">
-        <v>206</v>
-      </c>
-      <c r="C63" s="84"/>
-      <c r="D63" s="84"/>
-      <c r="E63" s="84"/>
-      <c r="F63" s="84"/>
-      <c r="G63" s="84"/>
-      <c r="H63" s="84"/>
-      <c r="I63" s="84"/>
-      <c r="J63" s="84"/>
-      <c r="K63" s="84"/>
-      <c r="L63" s="84"/>
-      <c r="M63" s="84"/>
-      <c r="N63" s="84"/>
-      <c r="O63" s="84"/>
+    <row r="64" spans="2:15" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="130" t="s">
+        <v>207</v>
+      </c>
+      <c r="C64" s="84"/>
+      <c r="D64" s="84"/>
+      <c r="E64" s="84"/>
+      <c r="F64" s="84"/>
+      <c r="G64" s="84"/>
+      <c r="H64" s="84"/>
+      <c r="I64" s="84"/>
+      <c r="J64" s="84"/>
+      <c r="K64" s="84"/>
+      <c r="L64" s="84"/>
+      <c r="M64" s="84"/>
+      <c r="N64" s="84"/>
+      <c r="O64" s="84"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="B61:G61"/>
+    <mergeCell ref="B63:G63"/>
     <mergeCell ref="B57:G57"/>
+    <mergeCell ref="B64:O64"/>
     <mergeCell ref="B56:G56"/>
     <mergeCell ref="B58:G58"/>
-    <mergeCell ref="B63:O63"/>
     <mergeCell ref="B62:G62"/>
     <mergeCell ref="B29:I29"/>
     <mergeCell ref="B59:G59"/>
@@ -17333,7 +17369,7 @@
     <mergeCell ref="B30:O30"/>
     <mergeCell ref="B55:G55"/>
   </mergeCells>
-  <conditionalFormatting sqref="B56:N62">
+  <conditionalFormatting sqref="B56:N63">
     <cfRule type="expression" dxfId="12" priority="2">
       <formula>$N56="Sí"</formula>
     </cfRule>
@@ -17417,7 +17453,7 @@
     </row>
     <row r="3" spans="2:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="16" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="2:20" ht="3" customHeight="1" x14ac:dyDescent="0.25">
@@ -17441,7 +17477,7 @@
     <row r="5" spans="2:20" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:20" ht="44.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="137" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C6" s="100"/>
       <c r="D6" s="100"/>
@@ -17461,15 +17497,15 @@
     </row>
     <row r="8" spans="2:20" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="31" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J8" s="31" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="9" spans="2:20" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="85" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C9" s="84"/>
       <c r="D9" s="84"/>
@@ -17480,13 +17516,13 @@
     </row>
     <row r="10" spans="2:20" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="20" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>180</v>
@@ -17498,7 +17534,7 @@
         <v>195</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="S10" s="26" t="s">
         <v>155</v>
@@ -17509,10 +17545,10 @@
     </row>
     <row r="11" spans="2:20" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="22" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D11" s="43">
         <v>-1.0746395942024931</v>
@@ -17541,10 +17577,10 @@
     </row>
     <row r="12" spans="2:20" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="C12" s="22" t="s">
         <v>218</v>
-      </c>
-      <c r="C12" s="22" t="s">
-        <v>217</v>
       </c>
       <c r="D12" s="43">
         <v>2.6058981057486798E-2</v>
@@ -17573,10 +17609,10 @@
     </row>
     <row r="13" spans="2:20" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="22" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D13" s="43">
         <v>-8.1688440081980769</v>
@@ -17605,10 +17641,10 @@
     </row>
     <row r="14" spans="2:20" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="22" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D14" s="43">
         <v>1.7524959269907161</v>
@@ -17637,10 +17673,10 @@
     </row>
     <row r="15" spans="2:20" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="22" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D15" s="43">
         <v>-0.10480581797991211</v>
@@ -17669,10 +17705,10 @@
     </row>
     <row r="16" spans="2:20" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="C16" s="22" t="s">
         <v>223</v>
-      </c>
-      <c r="C16" s="22" t="s">
-        <v>222</v>
       </c>
       <c r="D16" s="43">
         <v>0.46964279940151232</v>
@@ -17701,10 +17737,10 @@
     </row>
     <row r="17" spans="2:20" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="22" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D17" s="43">
         <v>-0.35314969903606419</v>
@@ -17733,10 +17769,10 @@
     </row>
     <row r="18" spans="2:20" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="22" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D18" s="43">
         <v>13.28718212898994</v>
@@ -17765,10 +17801,10 @@
     </row>
     <row r="19" spans="2:20" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="C19" s="22" t="s">
         <v>227</v>
-      </c>
-      <c r="C19" s="22" t="s">
-        <v>226</v>
       </c>
       <c r="D19" s="43">
         <v>-2.870836454563146</v>
@@ -17797,10 +17833,10 @@
     </row>
     <row r="20" spans="2:20" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="22" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D20" s="43">
         <v>-6.8802082327944687</v>
@@ -17829,10 +17865,10 @@
     </row>
     <row r="21" spans="2:20" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="22" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D21" s="43">
         <v>2.706978625157078</v>
@@ -17861,10 +17897,10 @@
     </row>
     <row r="22" spans="2:20" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="22" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D22" s="43">
         <v>14.689477533559799</v>
@@ -17893,12 +17929,12 @@
     </row>
     <row r="24" spans="2:20" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="31" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="25" spans="2:20" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="85" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C25" s="84"/>
       <c r="D25" s="84"/>
@@ -17909,13 +17945,13 @@
     </row>
     <row r="26" spans="2:20" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="20" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E26" s="20" t="s">
         <v>180</v>
@@ -17927,15 +17963,15 @@
         <v>195</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="27" spans="2:20" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="22" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D27" s="43">
         <v>-1.388127658491161</v>
@@ -17956,10 +17992,10 @@
     </row>
     <row r="28" spans="2:20" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="C28" s="22" t="s">
         <v>218</v>
-      </c>
-      <c r="C28" s="22" t="s">
-        <v>217</v>
       </c>
       <c r="D28" s="43">
         <v>5.50641707976623E-2</v>
@@ -17980,10 +18016,10 @@
     </row>
     <row r="29" spans="2:20" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="22" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D29" s="43">
         <v>-5.7791128775791032</v>
@@ -18004,10 +18040,10 @@
     </row>
     <row r="30" spans="2:20" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="22" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D30" s="43">
         <v>1.306626714669969</v>
@@ -18028,10 +18064,10 @@
     </row>
     <row r="31" spans="2:20" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="22" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D31" s="43">
         <v>-0.9814924809655684</v>
@@ -18052,10 +18088,10 @@
     </row>
     <row r="32" spans="2:20" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="C32" s="22" t="s">
         <v>223</v>
-      </c>
-      <c r="C32" s="22" t="s">
-        <v>222</v>
       </c>
       <c r="D32" s="43">
         <v>0.31605952452372271</v>
@@ -18076,10 +18112,10 @@
     </row>
     <row r="33" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="22" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D33" s="43">
         <v>0.505487843232863</v>
@@ -18100,10 +18136,10 @@
     </row>
     <row r="34" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="22" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D34" s="43">
         <v>10.150759128939161</v>
@@ -18124,10 +18160,10 @@
     </row>
     <row r="35" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="C35" s="22" t="s">
         <v>227</v>
-      </c>
-      <c r="C35" s="22" t="s">
-        <v>226</v>
       </c>
       <c r="D35" s="43">
         <v>0.47073111172229498</v>
@@ -18148,10 +18184,10 @@
     </row>
     <row r="36" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="22" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C36" s="22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D36" s="43">
         <v>-13.05213332185023</v>
@@ -18172,10 +18208,10 @@
     </row>
     <row r="37" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="22" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C37" s="22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D37" s="43">
         <v>-0.63741773773009991</v>
@@ -18196,10 +18232,10 @@
     </row>
     <row r="38" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="22" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D38" s="43">
         <v>11.71174502335024</v>
@@ -18220,10 +18256,10 @@
     </row>
     <row r="39" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="22" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D39" s="43">
         <v>15.70745347650818</v>
@@ -18244,10 +18280,10 @@
     </row>
     <row r="40" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="C40" s="22" t="s">
         <v>235</v>
-      </c>
-      <c r="C40" s="22" t="s">
-        <v>234</v>
       </c>
       <c r="D40" s="43">
         <v>34.958312471082372</v>
@@ -18268,12 +18304,12 @@
     </row>
     <row r="42" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="31" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="43" spans="2:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="85" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C43" s="84"/>
       <c r="D43" s="84"/>
@@ -18284,13 +18320,13 @@
     </row>
     <row r="44" spans="2:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="20" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D44" s="20" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E44" s="20" t="s">
         <v>180</v>
@@ -18302,15 +18338,15 @@
         <v>195</v>
       </c>
       <c r="H44" s="20" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="45" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="22" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C45" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D45" s="43">
         <v>3.409179056076526</v>
@@ -18331,10 +18367,10 @@
     </row>
     <row r="46" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="C46" s="22" t="s">
         <v>218</v>
-      </c>
-      <c r="C46" s="22" t="s">
-        <v>217</v>
       </c>
       <c r="D46" s="43">
         <v>0.104929139242267</v>
@@ -18355,10 +18391,10 @@
     </row>
     <row r="47" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="22" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D47" s="43">
         <v>1.455732240490484</v>
@@ -18379,10 +18415,10 @@
     </row>
     <row r="48" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="22" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C48" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D48" s="43">
         <v>4.4223471695821868</v>
@@ -18403,10 +18439,10 @@
     </row>
     <row r="49" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="22" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D49" s="43">
         <v>0.38608283181819208</v>
@@ -18427,10 +18463,10 @@
     </row>
     <row r="50" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="C50" s="22" t="s">
         <v>223</v>
-      </c>
-      <c r="C50" s="22" t="s">
-        <v>222</v>
       </c>
       <c r="D50" s="43">
         <v>-0.5427502597611743</v>
@@ -18451,10 +18487,10 @@
     </row>
     <row r="51" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="22" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D51" s="43">
         <v>-0.34876224091958469</v>
@@ -18475,10 +18511,10 @@
     </row>
     <row r="52" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="22" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D52" s="43">
         <v>0.3712676280070118</v>
@@ -18499,10 +18535,10 @@
     </row>
     <row r="53" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="C53" s="22" t="s">
         <v>227</v>
-      </c>
-      <c r="C53" s="22" t="s">
-        <v>226</v>
       </c>
       <c r="D53" s="43">
         <v>3.8506206188505412</v>
@@ -18523,10 +18559,10 @@
     </row>
     <row r="54" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="22" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C54" s="22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D54" s="43">
         <v>2.9020601096168628</v>
@@ -18547,10 +18583,10 @@
     </row>
     <row r="55" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="22" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C55" s="22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D55" s="43">
         <v>-3.078403827929256</v>
@@ -18571,10 +18607,10 @@
     </row>
     <row r="56" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="22" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C56" s="22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D56" s="43">
         <v>0.65686613874173283</v>
@@ -18595,12 +18631,12 @@
     </row>
     <row r="58" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="31" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="59" spans="2:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="85" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C59" s="84"/>
       <c r="D59" s="84"/>
@@ -18611,13 +18647,13 @@
     </row>
     <row r="60" spans="2:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="20" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D60" s="20" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E60" s="20" t="s">
         <v>180</v>
@@ -18629,15 +18665,15 @@
         <v>195</v>
       </c>
       <c r="H60" s="20" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="61" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="22" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C61" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D61" s="43">
         <v>3.8632814603939858</v>
@@ -18658,10 +18694,10 @@
     </row>
     <row r="62" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="C62" s="22" t="s">
         <v>218</v>
-      </c>
-      <c r="C62" s="22" t="s">
-        <v>217</v>
       </c>
       <c r="D62" s="43">
         <v>3.8024159363124602E-2</v>
@@ -18682,10 +18718,10 @@
     </row>
     <row r="63" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="22" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C63" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D63" s="43">
         <v>-0.69003162340262902</v>
@@ -18706,10 +18742,10 @@
     </row>
     <row r="64" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="22" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C64" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D64" s="43">
         <v>-2.228854100789575</v>
@@ -18730,10 +18766,10 @@
     </row>
     <row r="65" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="22" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C65" s="22" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D65" s="43">
         <v>-0.86775179212014697</v>
@@ -18754,10 +18790,10 @@
     </row>
     <row r="66" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="C66" s="22" t="s">
         <v>223</v>
-      </c>
-      <c r="C66" s="22" t="s">
-        <v>222</v>
       </c>
       <c r="D66" s="43">
         <v>-3.7188774649519999E-3</v>
@@ -18778,10 +18814,10 @@
     </row>
     <row r="67" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="22" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C67" s="22" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D67" s="43">
         <v>0.50503356227431406</v>
@@ -18802,10 +18838,10 @@
     </row>
     <row r="68" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="22" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C68" s="22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D68" s="43">
         <v>2.9441098337290188</v>
@@ -18826,10 +18862,10 @@
     </row>
     <row r="69" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="C69" s="22" t="s">
         <v>227</v>
-      </c>
-      <c r="C69" s="22" t="s">
-        <v>226</v>
       </c>
       <c r="D69" s="43">
         <v>4.326465724749621</v>
@@ -18850,10 +18886,10 @@
     </row>
     <row r="70" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="22" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C70" s="22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D70" s="43">
         <v>1.0960096259243881</v>
@@ -18874,10 +18910,10 @@
     </row>
     <row r="71" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="22" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C71" s="22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D71" s="43">
         <v>1.3232875458080191</v>
@@ -18898,10 +18934,10 @@
     </row>
     <row r="72" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="22" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C72" s="22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D72" s="43">
         <v>1.0387069145284</v>
@@ -18922,12 +18958,12 @@
     </row>
     <row r="74" spans="2:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="31" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="75" spans="2:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="85" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C75" s="84"/>
       <c r="D75" s="84"/>
@@ -18938,13 +18974,13 @@
     </row>
     <row r="76" spans="2:8" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="20" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C76" s="20" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D76" s="20" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E76" s="20" t="s">
         <v>180</v>
@@ -18956,15 +18992,15 @@
         <v>195</v>
       </c>
       <c r="H76" s="20" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="77" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="22" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C77" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D77" s="43">
         <v>-0.82914644330195753</v>
@@ -18985,10 +19021,10 @@
     </row>
     <row r="78" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="C78" s="22" t="s">
         <v>218</v>
-      </c>
-      <c r="C78" s="22" t="s">
-        <v>217</v>
       </c>
       <c r="D78" s="43">
         <v>3.1480352320405101E-2</v>
@@ -19009,10 +19045,10 @@
     </row>
     <row r="79" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="22" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C79" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D79" s="43">
         <v>-4.2464178462378817</v>
@@ -19033,10 +19069,10 @@
     </row>
     <row r="80" spans="2:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="22" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C80" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D80" s="43">
         <v>2.713991432127282</v>
@@ -19057,10 +19093,10 @@
     </row>
     <row r="81" spans="2:10" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="22" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C81" s="22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D81" s="43">
         <v>12.33332886927586</v>
@@ -19081,10 +19117,10 @@
     </row>
     <row r="82" spans="2:10" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="C82" s="22" t="s">
         <v>227</v>
-      </c>
-      <c r="C82" s="22" t="s">
-        <v>226</v>
       </c>
       <c r="D82" s="43">
         <v>-2.8017534476651171</v>
@@ -19105,10 +19141,10 @@
     </row>
     <row r="83" spans="2:10" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B83" s="22" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C83" s="22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D83" s="43">
         <v>-7.0628423604679886</v>
@@ -19129,10 +19165,10 @@
     </row>
     <row r="84" spans="2:10" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="22" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C84" s="22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D84" s="43">
         <v>3.250441027078304</v>
@@ -19153,10 +19189,10 @@
     </row>
     <row r="85" spans="2:10" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="22" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C85" s="22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D85" s="43">
         <v>15.42813920804759</v>
@@ -19177,12 +19213,12 @@
     </row>
     <row r="87" spans="2:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="31" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="88" spans="2:10" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="85" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C88" s="84"/>
       <c r="D88" s="84"/>
@@ -19193,30 +19229,30 @@
     </row>
     <row r="89" spans="2:10" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B89" s="20" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C89" s="20" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D89" s="20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E89" s="20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F89" s="20" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G89" s="20" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="90" spans="2:10" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B90" s="22" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C90" s="22" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D90" s="44">
         <v>-0.12693873106287509</v>
@@ -19234,10 +19270,10 @@
     </row>
     <row r="91" spans="2:10" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="C91" s="22" t="s">
         <v>223</v>
-      </c>
-      <c r="C91" s="22" t="s">
-        <v>222</v>
       </c>
       <c r="D91" s="44">
         <v>0.47221026245675668</v>
@@ -19255,10 +19291,10 @@
     </row>
     <row r="92" spans="2:10" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" s="22" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C92" s="22" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D92" s="44">
         <v>-0.36726030146356048</v>
@@ -19276,10 +19312,10 @@
     </row>
     <row r="93" spans="2:10" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B93" s="22" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C93" s="22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D93" s="44">
         <v>13.29019625269507</v>
@@ -19297,10 +19333,10 @@
     </row>
     <row r="94" spans="2:10" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B94" s="22" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C94" s="22" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D94" s="44">
         <v>15.044018037333471</v>
@@ -19318,15 +19354,15 @@
     </row>
     <row r="96" spans="2:10" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B96" s="31" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J96" s="31" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="97" spans="2:17" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B97" s="85" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C97" s="84"/>
       <c r="D97" s="84"/>
@@ -19337,27 +19373,27 @@
     </row>
     <row r="98" spans="2:17" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B98" s="20" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C98" s="20" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D98" s="20" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E98" s="20" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F98" s="20" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="99" spans="2:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B99" s="22" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C99" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D99" s="46">
         <v>0.60857857206665189</v>
@@ -19371,10 +19407,10 @@
     </row>
     <row r="100" spans="2:17" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B100" s="22" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C100" s="45" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D100" s="46">
         <v>0.61132599309468094</v>
@@ -19388,10 +19424,10 @@
     </row>
     <row r="101" spans="2:17" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B101" s="22" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C101" s="45" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D101" s="46">
         <v>0.65462771238238304</v>
@@ -19405,10 +19441,10 @@
     </row>
     <row r="102" spans="2:17" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B102" s="22" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C102" s="45" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D102" s="46">
         <v>0.65644797939783128</v>
@@ -19422,10 +19458,10 @@
     </row>
     <row r="103" spans="2:17" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B103" s="22" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C103" s="45" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D103" s="46">
         <v>0.75482084489177625</v>
@@ -19439,10 +19475,10 @@
     </row>
     <row r="104" spans="2:17" ht="54.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B104" s="22" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C104" s="45" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D104" s="46">
         <v>0.78249761812761076</v>
@@ -19456,7 +19492,7 @@
     </row>
     <row r="106" spans="2:17" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B106" s="130" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C106" s="84"/>
       <c r="D106" s="84"/>
@@ -19575,12 +19611,12 @@
     </row>
     <row r="2" spans="2:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="15" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" spans="2:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="16" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="2:13" ht="3" customHeight="1" x14ac:dyDescent="0.25">
@@ -19600,12 +19636,12 @@
     <row r="5" spans="2:13" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="31" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="2:13" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="85" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C7" s="84"/>
       <c r="D7" s="84"/>
@@ -19617,19 +19653,19 @@
     </row>
     <row r="8" spans="2:13" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="20" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G8" s="20" t="s">
         <v>180</v>
@@ -19649,7 +19685,7 @@
     </row>
     <row r="9" spans="2:13" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="22" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C9" s="47">
         <v>0.20599999999999999</v>
@@ -19662,7 +19698,7 @@
         <v>-7.7999999999999989</v>
       </c>
       <c r="F9" s="50" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G9" s="49"/>
       <c r="H9" s="49"/>
@@ -19670,7 +19706,7 @@
     </row>
     <row r="10" spans="2:13" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="22" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C10" s="47">
         <v>0.63500000000000001</v>
@@ -19705,7 +19741,7 @@
     </row>
     <row r="11" spans="2:13" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="22" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C11" s="47">
         <v>0.71900000000000008</v>
@@ -19740,7 +19776,7 @@
     </row>
     <row r="12" spans="2:13" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="22" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C12" s="47">
         <v>0.59200000000000008</v>
@@ -19775,7 +19811,7 @@
     </row>
     <row r="13" spans="2:13" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="130" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C13" s="84"/>
       <c r="D13" s="84"/>
@@ -19787,20 +19823,20 @@
     </row>
     <row r="15" spans="2:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="31" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="34" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="31" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="35" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="85" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C35" s="84"/>
       <c r="D35" s="84"/>
@@ -19815,22 +19851,22 @@
         <v>85</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D36" s="20" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F36" s="20" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G36" s="20" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H36" s="20" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="37" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -20310,12 +20346,12 @@
     </row>
     <row r="57" spans="2:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="31" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="58" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="85" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C58" s="84"/>
       <c r="D58" s="84"/>
@@ -20327,10 +20363,10 @@
     </row>
     <row r="59" spans="2:9" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="20" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D59" s="20" t="s">
         <v>180</v>
@@ -20342,17 +20378,17 @@
         <v>195</v>
       </c>
       <c r="G59" s="20" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="60" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="54" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="61" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="55" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C61" s="44">
         <v>6.4682899567040124</v>
@@ -20373,7 +20409,7 @@
     </row>
     <row r="62" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="55" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C62" s="44">
         <v>-8.4536540512359995E-3</v>
@@ -20394,7 +20430,7 @@
     </row>
     <row r="63" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="55" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C63" s="44">
         <v>1.5055406666880951</v>
@@ -20415,7 +20451,7 @@
     </row>
     <row r="64" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="55" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C64" s="44">
         <v>2.4520120263858969</v>
@@ -20436,12 +20472,12 @@
     </row>
     <row r="65" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="54" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="66" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="55" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C66" s="44">
         <v>18.01970515501932</v>
@@ -20462,7 +20498,7 @@
     </row>
     <row r="67" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="55" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C67" s="44">
         <v>-0.31917353065088749</v>
@@ -20483,7 +20519,7 @@
     </row>
     <row r="68" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="55" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C68" s="44">
         <v>0.40011607971187141</v>
@@ -20504,7 +20540,7 @@
     </row>
     <row r="69" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="55" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C69" s="44">
         <v>2.6948940586949881</v>
@@ -20525,12 +20561,12 @@
     </row>
     <row r="70" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="54" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="71" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="55" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C71" s="44">
         <v>9.2810294480686597</v>
@@ -20551,7 +20587,7 @@
     </row>
     <row r="72" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="55" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C72" s="44">
         <v>0.49827179282514161</v>
@@ -20572,7 +20608,7 @@
     </row>
     <row r="73" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="55" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C73" s="44">
         <v>-5.1024284221668754</v>
@@ -20593,7 +20629,7 @@
     </row>
     <row r="74" spans="2:9" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="55" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C74" s="44">
         <v>19.499487649067682</v>
@@ -20614,7 +20650,7 @@
     </row>
     <row r="76" spans="2:9" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="130" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C76" s="84"/>
       <c r="D76" s="84"/>
@@ -20721,12 +20757,12 @@
     </row>
     <row r="2" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="15" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="16" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4" spans="2:14" ht="3" customHeight="1" x14ac:dyDescent="0.25">
@@ -20747,7 +20783,7 @@
     <row r="5" spans="2:14" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="31" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7" spans="2:14" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -20755,48 +20791,48 @@
         <v>98</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I7" s="20" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J7" s="20" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K7" s="20" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L7" s="20" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M7" s="20" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N7" s="20" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="8" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="56" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C8" s="57" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D8" s="58">
         <v>67633</v>
@@ -20836,10 +20872,10 @@
     </row>
     <row r="9" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="21" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D9" s="23">
         <v>7009</v>
@@ -20879,10 +20915,10 @@
     </row>
     <row r="10" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="21" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D10" s="23">
         <v>2415</v>
@@ -20922,10 +20958,10 @@
     </row>
     <row r="11" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="21" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D11" s="23">
         <v>5349</v>
@@ -20965,10 +21001,10 @@
     </row>
     <row r="12" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="21" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D12" s="23">
         <v>684</v>
@@ -21008,10 +21044,10 @@
     </row>
     <row r="13" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="21" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D13" s="23">
         <v>19167</v>
@@ -21049,10 +21085,10 @@
     </row>
     <row r="14" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="21" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D14" s="23">
         <v>23854</v>
@@ -21092,10 +21128,10 @@
     </row>
     <row r="15" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="21" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D15" s="23">
         <v>3593</v>
@@ -21135,7 +21171,7 @@
     </row>
     <row r="16" spans="2:14" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="130" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C16" s="84"/>
       <c r="D16" s="84"/>
@@ -21152,12 +21188,12 @@
     </row>
     <row r="18" spans="2:2" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="31" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="40" spans="2:12" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="31" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="41" spans="2:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -21165,42 +21201,42 @@
         <v>98</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D41" s="20" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E41" s="20" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F41" s="20" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G41" s="20" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H41" s="20" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I41" s="20" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J41" s="20" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K41" s="20" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L41" s="20" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="42" spans="2:12" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="56" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C42" s="57" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D42" s="61">
         <f t="shared" ref="D42:L42" si="2">IF(D8="","",D8/$D8*100)</f>
@@ -21241,10 +21277,10 @@
     </row>
     <row r="43" spans="2:12" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="21" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C43" s="22" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D43" s="62">
         <f t="shared" ref="D43:L43" si="3">IF(D9="","",D9/$D9*100)</f>
@@ -21285,10 +21321,10 @@
     </row>
     <row r="44" spans="2:12" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="21" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C44" s="22" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D44" s="62">
         <f t="shared" ref="D44:L44" si="4">IF(D10="","",D10/$D10*100)</f>
@@ -21329,10 +21365,10 @@
     </row>
     <row r="45" spans="2:12" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="21" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C45" s="22" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D45" s="62">
         <f t="shared" ref="D45:L45" si="5">IF(D11="","",D11/$D11*100)</f>
@@ -21373,10 +21409,10 @@
     </row>
     <row r="46" spans="2:12" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="21" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C46" s="22" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D46" s="62">
         <f t="shared" ref="D46:L46" si="6">IF(D12="","",D12/$D12*100)</f>
@@ -21417,10 +21453,10 @@
     </row>
     <row r="47" spans="2:12" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="21" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D47" s="62">
         <f t="shared" ref="D47:L47" si="7">IF(D13="","",D13/$D13*100)</f>
@@ -21461,10 +21497,10 @@
     </row>
     <row r="48" spans="2:12" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="56" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C48" s="57" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D48" s="61">
         <f t="shared" ref="D48:L48" si="8">IF(D14="","",D14/$D14*100)</f>
@@ -21505,10 +21541,10 @@
     </row>
     <row r="49" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="56" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C49" s="57" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D49" s="61">
         <f t="shared" ref="D49:L49" si="9">IF(D15="","",D15/$D15*100)</f>
@@ -21549,7 +21585,7 @@
     </row>
     <row r="50" spans="2:14" ht="19.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="130" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C50" s="84"/>
       <c r="D50" s="84"/>
@@ -21566,48 +21602,48 @@
     </row>
     <row r="52" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="31" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="53" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="20"/>
       <c r="C53" s="20" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D53" s="20" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F53" s="20" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G53" s="20" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H53" s="20" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I53" s="20" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J53" s="20" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K53" s="20" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L53" s="20" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="54" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="21" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C54" s="22" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D54" s="23">
         <v>170219</v>
@@ -21639,10 +21675,10 @@
     </row>
     <row r="55" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="21" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C55" s="22" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D55" s="23">
         <v>67633</v>
@@ -21674,10 +21710,10 @@
     </row>
     <row r="56" spans="2:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="56" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C56" s="57" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D56" s="63">
         <f t="shared" ref="D56:L56" si="10">D54/D55</f>
@@ -21718,7 +21754,7 @@
     </row>
     <row r="57" spans="2:14" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="130" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C57" s="84"/>
       <c r="D57" s="84"/>
@@ -21827,12 +21863,12 @@
     </row>
     <row r="2" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="15" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="3" spans="2:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="16" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="2:21" ht="3" customHeight="1" x14ac:dyDescent="0.25">
@@ -21855,15 +21891,15 @@
     <row r="5" spans="2:21" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="7" spans="2:21" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="139" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C7" s="96"/>
       <c r="D7" s="96"/>
@@ -21873,23 +21909,23 @@
       </c>
       <c r="G7" s="143"/>
       <c r="I7" s="138" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J7" s="84"/>
       <c r="K7" s="17"/>
       <c r="L7" s="138" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M7" s="84"/>
       <c r="N7" s="17"/>
       <c r="O7" s="138" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P7" s="84"/>
     </row>
     <row r="8" spans="2:21" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="139" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C8" s="96"/>
       <c r="D8" s="96"/>
@@ -21904,7 +21940,7 @@
       </c>
       <c r="J8" s="84"/>
       <c r="K8" s="64" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L8" s="144">
         <f>E14</f>
@@ -21920,17 +21956,17 @@
     </row>
     <row r="9" spans="2:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="139" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C9" s="96"/>
       <c r="D9" s="96"/>
       <c r="E9" s="96"/>
       <c r="F9" s="148" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G9" s="143"/>
       <c r="I9" s="146" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J9" s="84"/>
       <c r="K9" s="84"/>
@@ -21945,7 +21981,7 @@
     </row>
     <row r="10" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="114" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C10" s="84"/>
       <c r="D10" s="84"/>
@@ -21953,7 +21989,7 @@
       <c r="F10" s="84"/>
       <c r="G10" s="84"/>
       <c r="I10" s="141" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J10" s="84"/>
       <c r="K10" s="84"/>
@@ -21967,10 +22003,10 @@
     </row>
     <row r="12" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="13" spans="2:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -21981,34 +22017,34 @@
         <v>85</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="R13" s="26" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="S13" s="26" t="s">
         <v>84</v>
       </c>
       <c r="T13" s="26" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="U13" s="26" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="14" spans="2:21" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="66"/>
       <c r="C14" s="67" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D14" s="68">
         <f>SUMIFS(Datos_escenarios!$E$8:$E$67,Datos_escenarios!$B$8:$B$67,grupo_sim,Datos_escenarios!$C$8:$C$67,0)</f>
@@ -22770,7 +22806,7 @@
     </row>
     <row r="35" spans="2:21" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="147" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C35" s="89"/>
       <c r="D35" s="89"/>
@@ -22789,7 +22825,7 @@
     </row>
     <row r="36" spans="2:21" ht="44.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="145" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C36" s="89"/>
       <c r="D36" s="89"/>
